--- a/month-1-excel-sql/excel/practical-files/shopee_dataset.csv.xlsx
+++ b/month-1-excel-sql/excel/practical-files/shopee_dataset.csv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyPc\OneDrive\Desktop\File Ezzamie\Supply Chain\supply-chain-learning\month-1-excel-sql\excel\practical-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADED545A-3F70-4F0B-8DC7-186D678B879B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E6F5E4-3C88-4C84-87C3-0EF4BB174B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{853F661C-3DAD-4ABE-A156-A3D937B1C445}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{853F661C-3DAD-4ABE-A156-A3D937B1C445}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales by Category" sheetId="4" r:id="rId1"/>
@@ -22,13 +22,13 @@
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="2" r:id="rId7"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="114">
   <si>
     <t>OrderID</t>
   </si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>Sum of Revenue Retentation %</t>
+  </si>
+  <si>
+    <t>Sum of Avg Order Value</t>
   </si>
 </sst>
 </file>
@@ -509,7 +512,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -695,12 +698,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -862,7 +859,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -875,12 +872,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -926,7 +920,21 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -997,6 +1005,20 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1015,7 +1037,7 @@
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:N1048576" sheet="shopee_dataset"/>
   </cacheSource>
-  <cacheFields count="15">
+  <cacheFields count="16">
     <cacheField name="OrderID" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
@@ -1087,6 +1109,7 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="3" maxValue="5"/>
     </cacheField>
     <cacheField name="Revenue Retentation %" numFmtId="0" formula="NetSales/GrossSales" databaseField="0"/>
+    <cacheField name="Avg Order Value" numFmtId="0" formula="NetSales /Quantity" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -1758,9 +1781,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47B73B61-D695-4114-A985-E65ACD861D36}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47B73B61-D695-4114-A985-E65ACD861D36}" name="PivotTable5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
+  <pivotFields count="16">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -1787,6 +1810,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="4"/>
@@ -1833,7 +1857,7 @@
     <dataField name="Sum of Quantity" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="9">
+    <format dxfId="13">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -1842,7 +1866,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="8">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -1865,16 +1889,16 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{66BFE013-0FCF-4F3F-8A52-8225F8DEE280}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:D10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{66BFE013-0FCF-4F3F-8A52-8225F8DEE280}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:F10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="16">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -1893,6 +1917,7 @@
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="10"/>
@@ -1923,7 +1948,7 @@
   <colFields count="1">
     <field x="-2"/>
   </colFields>
-  <colItems count="3">
+  <colItems count="5">
     <i>
       <x/>
     </i>
@@ -1933,14 +1958,22 @@
     <i i="2">
       <x v="2"/>
     </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
   </colItems>
-  <dataFields count="3">
+  <dataFields count="5">
     <dataField name="Sum of NetSales" fld="9" baseField="0" baseItem="0"/>
     <dataField name="Average of Rating" fld="13" subtotal="average" baseField="10" baseItem="0"/>
     <dataField name="Count of OrderID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Quantity" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Avg Order Value" fld="15" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="7">
+    <format dxfId="11">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="1">
@@ -1949,7 +1982,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="1">
@@ -1972,9 +2005,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3670484D-4D0F-4E31-8764-937C29AA622C}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3670484D-4D0F-4E31-8764-937C29AA622C}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C32" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
+  <pivotFields count="16">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -2011,6 +2044,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="11"/>
@@ -2120,8 +2154,8 @@
     <dataField name="Sum of NetSales" fld="9" baseField="0" baseItem="0"/>
     <dataField name="Count of OrderID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="4">
-    <format dxfId="5">
+  <formats count="2">
+    <format dxfId="9">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="11" count="1">
@@ -2130,34 +2164,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="11" count="1">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="3">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
-          <reference field="4" count="1">
-            <x v="2"/>
-          </reference>
-          <reference field="11" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="2">
-          <reference field="4" count="1">
-            <x v="2"/>
-          </reference>
-          <reference field="11" count="1" selected="0">
             <x v="3"/>
           </reference>
         </references>
@@ -2177,9 +2187,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B9A7F9E9-3DE2-4EE1-AC8D-3AFC549CEE3F}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B9A7F9E9-3DE2-4EE1-AC8D-3AFC549CEE3F}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
+  <pivotFields count="16">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -2204,6 +2214,7 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="12"/>
@@ -2244,7 +2255,7 @@
     <dataField name="Sum of NetSales" fld="9" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="1">
+    <format dxfId="7">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="12" count="1">
@@ -2253,7 +2264,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="12" count="1">
@@ -2276,9 +2287,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{760AEA23-AE5D-4D22-9A17-89CFCA155483}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{760AEA23-AE5D-4D22-9A17-89CFCA155483}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
+  <pivotFields count="16">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -2305,6 +2316,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="4"/>
@@ -2676,11 +2688,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -2697,10 +2709,10 @@
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>2218.6</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="7">
         <v>24</v>
       </c>
     </row>
@@ -2708,10 +2720,10 @@
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>284.5</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="7">
         <v>9</v>
       </c>
     </row>
@@ -2719,10 +2731,10 @@
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="8">
         <v>3158.4</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="8">
         <v>43</v>
       </c>
     </row>
@@ -2730,10 +2742,10 @@
       <c r="A7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>905.3</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="7">
         <v>14</v>
       </c>
     </row>
@@ -2741,10 +2753,10 @@
       <c r="A8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>331.7</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="7">
         <v>11</v>
       </c>
     </row>
@@ -2752,10 +2764,10 @@
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>998.80000000000007</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="7">
         <v>11</v>
       </c>
     </row>
@@ -2763,15 +2775,17 @@
       <c r="A10" s="3" t="s">
         <v>99</v>
       </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>7897.3</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="7">
         <v>112</v>
       </c>
     </row>
@@ -2782,23 +2796,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76C707AF-4C8E-4CF1-A191-926FF07CD046}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>98</v>
       </c>
@@ -2811,94 +2827,143 @@
       <c r="D3" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>1519.5</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="7">
         <v>3.8571428571428572</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="7">
+        <v>18</v>
+      </c>
+      <c r="F4" s="7">
+        <v>84.416666666666671</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>1208.2</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="7">
         <v>3.8</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="7">
+        <v>14</v>
+      </c>
+      <c r="F5" s="7">
+        <v>86.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="8">
         <v>2478.3000000000002</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="8">
         <v>4.083333333333333</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="8">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="8">
+        <v>36</v>
+      </c>
+      <c r="F6" s="8">
+        <v>68.841666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>1459.1999999999998</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="7">
         <v>3.8571428571428572</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" s="7">
+        <v>22</v>
+      </c>
+      <c r="F7" s="7">
+        <v>66.327272727272714</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>1232.1000000000001</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="7">
         <v>4.1111111111111107</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="7">
+        <v>22</v>
+      </c>
+      <c r="F8" s="7">
+        <v>56.004545454545458</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <v>7897.3</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="7">
         <v>3.9750000000000001</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="7">
         <v>40</v>
+      </c>
+      <c r="E10" s="7">
+        <v>112</v>
+      </c>
+      <c r="F10" s="7">
+        <v>70.511607142857144</v>
       </c>
     </row>
   </sheetData>
@@ -2917,11 +2982,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -2938,10 +3003,10 @@
       <c r="A4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>1519.1999999999998</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="7">
         <v>9</v>
       </c>
     </row>
@@ -2949,10 +3014,10 @@
       <c r="A5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>119.6</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="7">
         <v>1</v>
       </c>
     </row>
@@ -2960,10 +3025,10 @@
       <c r="A6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>59.7</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="7">
         <v>1</v>
       </c>
     </row>
@@ -2971,10 +3036,10 @@
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>398.6</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="7">
         <v>3</v>
       </c>
     </row>
@@ -2982,10 +3047,10 @@
       <c r="A8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>179.6</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="7">
         <v>2</v>
       </c>
     </row>
@@ -2993,10 +3058,10 @@
       <c r="A9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>174.7</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3004,10 +3069,10 @@
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <v>587</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3015,10 +3080,10 @@
       <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>1892.4</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="7">
         <v>10</v>
       </c>
     </row>
@@ -3026,10 +3091,10 @@
       <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="7">
         <v>558.5</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="7">
         <v>2</v>
       </c>
     </row>
@@ -3037,10 +3102,10 @@
       <c r="A13" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <v>224.8</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="7">
         <v>2</v>
       </c>
     </row>
@@ -3048,10 +3113,10 @@
       <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <v>916.9</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="7">
         <v>4</v>
       </c>
     </row>
@@ -3059,10 +3124,10 @@
       <c r="A15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="7">
         <v>12.5</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3070,10 +3135,10 @@
       <c r="A16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="7">
         <v>179.7</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3081,10 +3146,10 @@
       <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="7">
         <v>1738.6000000000001</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="7">
         <v>7</v>
       </c>
     </row>
@@ -3092,10 +3157,10 @@
       <c r="A18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="7">
         <v>1093</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="7">
         <v>2</v>
       </c>
     </row>
@@ -3103,10 +3168,10 @@
       <c r="A19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="7">
         <v>198.6</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="7">
         <v>3</v>
       </c>
     </row>
@@ -3114,10 +3179,10 @@
       <c r="A20" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="7">
         <v>444.5</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3125,10 +3190,10 @@
       <c r="A21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="7">
         <v>2.5</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3136,10 +3201,10 @@
       <c r="A22" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="8">
         <v>2022.2</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="8">
         <v>12</v>
       </c>
     </row>
@@ -3147,21 +3212,21 @@
       <c r="A23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="7">
         <v>447.5</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="7">
         <v>919.40000000000009</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="7">
         <v>5</v>
       </c>
     </row>
@@ -3169,10 +3234,10 @@
       <c r="A25" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="7">
         <v>268.7</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="7">
         <v>2</v>
       </c>
     </row>
@@ -3180,10 +3245,10 @@
       <c r="A26" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="7">
         <v>157</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="7">
         <v>2</v>
       </c>
     </row>
@@ -3191,10 +3256,10 @@
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="7">
         <v>229.6</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3202,10 +3267,10 @@
       <c r="A28" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="7">
         <v>724.9</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="7">
         <v>2</v>
       </c>
     </row>
@@ -3213,10 +3278,10 @@
       <c r="A29" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="7">
         <v>724.9</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="7">
         <v>2</v>
       </c>
     </row>
@@ -3224,20 +3289,24 @@
       <c r="A30" s="3" t="s">
         <v>99</v>
       </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>99</v>
       </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="7">
         <v>7897.2999999999984</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="7">
         <v>40</v>
       </c>
     </row>
@@ -3257,10 +3326,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="9"/>
+      <c r="B1" s="6"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -3277,10 +3346,10 @@
       <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>9</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="7">
         <v>1977.8</v>
       </c>
     </row>
@@ -3288,10 +3357,10 @@
       <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>8</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="7">
         <v>915</v>
       </c>
     </row>
@@ -3299,10 +3368,10 @@
       <c r="A6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="8">
         <v>14</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="8">
         <v>2562.1000000000004</v>
       </c>
     </row>
@@ -3310,10 +3379,10 @@
       <c r="A7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>9</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="7">
         <v>2442.3999999999996</v>
       </c>
     </row>
@@ -3321,15 +3390,17 @@
       <c r="A8" s="3" t="s">
         <v>99</v>
       </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>40</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="7">
         <v>7897.3000000000011</v>
       </c>
     </row>
@@ -3376,16 +3447,16 @@
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>2258.6</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="7">
         <v>2218.6</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="7">
         <v>5.7142857142857144</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="7">
         <v>0.98228991410608346</v>
       </c>
     </row>
@@ -3393,16 +3464,16 @@
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>289.5</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="7">
         <v>284.5</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="7">
         <v>1.6666666666666667</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="7">
         <v>0.98272884283246975</v>
       </c>
     </row>
@@ -3410,16 +3481,16 @@
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>3263.4</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="7">
         <v>3158.4</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="7">
         <v>6.1764705882352944</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="7">
         <v>0.96782496782496785</v>
       </c>
     </row>
@@ -3427,16 +3498,16 @@
       <c r="A7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>930.3</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="7">
         <v>905.3</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="7">
         <v>4.166666666666667</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="7">
         <v>0.97312694829624857</v>
       </c>
     </row>
@@ -3444,16 +3515,16 @@
       <c r="A8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>366.7</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="7">
         <v>331.7</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="7">
         <v>11.666666666666666</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="7">
         <v>0.90455413144259611</v>
       </c>
     </row>
@@ -3461,16 +3532,16 @@
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>1028.8</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="7">
         <v>998.80000000000007</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="7">
         <v>7.5</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="7">
         <v>0.97083981337480574</v>
       </c>
     </row>
@@ -3478,7 +3549,10 @@
       <c r="A10" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E10" t="e">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7" t="e">
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3486,16 +3560,16 @@
       <c r="A11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>8137.2999999999993</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="7">
         <v>7897.2999999999993</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="7">
         <v>6</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="7">
         <v>0.97050618755606899</v>
       </c>
     </row>

--- a/month-1-excel-sql/excel/practical-files/shopee_dataset.csv.xlsx
+++ b/month-1-excel-sql/excel/practical-files/shopee_dataset.csv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyPc\OneDrive\Desktop\File Ezzamie\Supply Chain\supply-chain-learning\month-1-excel-sql\excel\practical-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E6F5E4-3C88-4C84-87C3-0EF4BB174B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77012EA-372A-40FB-BD60-DDF6D31514C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{853F661C-3DAD-4ABE-A156-A3D937B1C445}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{853F661C-3DAD-4ABE-A156-A3D937B1C445}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales by Category" sheetId="4" r:id="rId1"/>
@@ -19,16 +19,28 @@
     <sheet name="Payment Method Breakdown" sheetId="5" r:id="rId4"/>
     <sheet name="Discount Impact" sheetId="6" r:id="rId5"/>
     <sheet name="shopee_dataset" sheetId="1" r:id="rId6"/>
+    <sheet name="Seller_Lookup" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="120">
   <si>
     <t>OrderID</t>
   </si>
@@ -370,6 +382,24 @@
   </si>
   <si>
     <t>Sum of Avg Order Value</t>
+  </si>
+  <si>
+    <t>Tier</t>
+  </si>
+  <si>
+    <t>Commission %</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+  </si>
+  <si>
+    <t>Seller_Tier</t>
   </si>
 </sst>
 </file>
@@ -859,7 +889,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -872,9 +902,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -920,49 +951,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1109,7 +1098,7 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="3" maxValue="5"/>
     </cacheField>
     <cacheField name="Revenue Retentation %" numFmtId="0" formula="NetSales/GrossSales" databaseField="0"/>
-    <cacheField name="Avg Order Value" numFmtId="0" formula="NetSales /Quantity" databaseField="0"/>
+    <cacheField name="Avg Order Value" numFmtId="0" formula="NetSales/Quantity" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -1781,7 +1770,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47B73B61-D695-4114-A985-E65ACD861D36}" name="PivotTable5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47B73B61-D695-4114-A985-E65ACD861D36}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField showAll="0"/>
@@ -1857,7 +1846,7 @@
     <dataField name="Sum of Quantity" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="13">
+    <format dxfId="5">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -1866,7 +1855,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -1889,7 +1878,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{66BFE013-0FCF-4F3F-8A52-8225F8DEE280}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{66BFE013-0FCF-4F3F-8A52-8225F8DEE280}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:F10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField dataField="1" showAll="0"/>
@@ -1973,7 +1962,7 @@
     <dataField name="Sum of Avg Order Value" fld="15" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="11">
+    <format dxfId="3">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="1">
@@ -1982,7 +1971,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="10" count="1">
@@ -2005,7 +1994,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3670484D-4D0F-4E31-8764-937C29AA622C}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3670484D-4D0F-4E31-8764-937C29AA622C}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C32" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField dataField="1" showAll="0"/>
@@ -2155,7 +2144,7 @@
     <dataField name="Count of OrderID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="9">
+    <format dxfId="7">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="11" count="1">
@@ -2164,7 +2153,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="8">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="11" count="1">
@@ -2187,7 +2176,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B9A7F9E9-3DE2-4EE1-AC8D-3AFC549CEE3F}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B9A7F9E9-3DE2-4EE1-AC8D-3AFC549CEE3F}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField dataField="1" showAll="0"/>
@@ -2255,7 +2244,7 @@
     <dataField name="Sum of NetSales" fld="9" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="7">
+    <format dxfId="1">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="12" count="1">
@@ -2264,7 +2253,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="12" count="1">
@@ -2287,7 +2276,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{760AEA23-AE5D-4D22-9A17-89CFCA155483}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{760AEA23-AE5D-4D22-9A17-89CFCA155483}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField showAll="0"/>
@@ -2688,11 +2677,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -2709,10 +2696,10 @@
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4">
         <v>2218.6</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4">
         <v>24</v>
       </c>
     </row>
@@ -2720,10 +2707,10 @@
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>284.5</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>9</v>
       </c>
     </row>
@@ -2731,10 +2718,10 @@
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>3158.4</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>43</v>
       </c>
     </row>
@@ -2742,10 +2729,10 @@
       <c r="A7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>905.3</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7">
         <v>14</v>
       </c>
     </row>
@@ -2753,10 +2740,10 @@
       <c r="A8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8">
         <v>331.7</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8">
         <v>11</v>
       </c>
     </row>
@@ -2764,10 +2751,10 @@
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>998.80000000000007</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9">
         <v>11</v>
       </c>
     </row>
@@ -2775,17 +2762,15 @@
       <c r="A10" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11">
         <v>7897.3</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11">
         <v>112</v>
       </c>
     </row>
@@ -2808,11 +2793,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -2838,19 +2821,19 @@
       <c r="A4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4">
         <v>1519.5</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4">
         <v>3.8571428571428572</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4">
         <v>7</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4">
         <v>18</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4">
         <v>84.416666666666671</v>
       </c>
     </row>
@@ -2858,19 +2841,19 @@
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>1208.2</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>3.8</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5">
         <v>5</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5">
         <v>14</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5">
         <v>86.3</v>
       </c>
     </row>
@@ -2878,19 +2861,19 @@
       <c r="A6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>2478.3000000000002</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>4.083333333333333</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>12</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <v>36</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="6">
         <v>68.841666666666669</v>
       </c>
     </row>
@@ -2898,19 +2881,19 @@
       <c r="A7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>1459.1999999999998</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7">
         <v>3.8571428571428572</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7">
         <v>7</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7">
         <v>22</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7">
         <v>66.327272727272714</v>
       </c>
     </row>
@@ -2918,19 +2901,19 @@
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8">
         <v>1232.1000000000001</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8">
         <v>4.1111111111111107</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8">
         <v>9</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8">
         <v>22</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8">
         <v>56.004545454545458</v>
       </c>
     </row>
@@ -2938,11 +2921,7 @@
       <c r="A9" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7" t="e">
+      <c r="F9" t="e">
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2950,19 +2929,19 @@
       <c r="A10" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10">
         <v>7897.3</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10">
         <v>3.9750000000000001</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10">
         <v>40</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10">
         <v>112</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10">
         <v>70.511607142857144</v>
       </c>
     </row>
@@ -2982,11 +2961,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -3003,10 +2980,10 @@
       <c r="A4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4">
         <v>1519.1999999999998</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4">
         <v>9</v>
       </c>
     </row>
@@ -3014,10 +2991,10 @@
       <c r="A5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>119.6</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>1</v>
       </c>
     </row>
@@ -3025,10 +3002,10 @@
       <c r="A6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>59.7</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6">
         <v>1</v>
       </c>
     </row>
@@ -3036,10 +3013,10 @@
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>398.6</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7">
         <v>3</v>
       </c>
     </row>
@@ -3047,10 +3024,10 @@
       <c r="A8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8">
         <v>179.6</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8">
         <v>2</v>
       </c>
     </row>
@@ -3058,10 +3035,10 @@
       <c r="A9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>174.7</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9">
         <v>1</v>
       </c>
     </row>
@@ -3069,10 +3046,10 @@
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10">
         <v>587</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10">
         <v>1</v>
       </c>
     </row>
@@ -3080,10 +3057,10 @@
       <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11">
         <v>1892.4</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11">
         <v>10</v>
       </c>
     </row>
@@ -3091,10 +3068,10 @@
       <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12">
         <v>558.5</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12">
         <v>2</v>
       </c>
     </row>
@@ -3102,10 +3079,10 @@
       <c r="A13" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13">
         <v>224.8</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13">
         <v>2</v>
       </c>
     </row>
@@ -3113,10 +3090,10 @@
       <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14">
         <v>916.9</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14">
         <v>4</v>
       </c>
     </row>
@@ -3124,10 +3101,10 @@
       <c r="A15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15">
         <v>12.5</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15">
         <v>1</v>
       </c>
     </row>
@@ -3135,10 +3112,10 @@
       <c r="A16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16">
         <v>179.7</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16">
         <v>1</v>
       </c>
     </row>
@@ -3146,10 +3123,10 @@
       <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17">
         <v>1738.6000000000001</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17">
         <v>7</v>
       </c>
     </row>
@@ -3157,10 +3134,10 @@
       <c r="A18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18">
         <v>1093</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18">
         <v>2</v>
       </c>
     </row>
@@ -3168,10 +3145,10 @@
       <c r="A19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19">
         <v>198.6</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19">
         <v>3</v>
       </c>
     </row>
@@ -3179,10 +3156,10 @@
       <c r="A20" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20">
         <v>444.5</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20">
         <v>1</v>
       </c>
     </row>
@@ -3190,10 +3167,10 @@
       <c r="A21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21">
         <v>2.5</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21">
         <v>1</v>
       </c>
     </row>
@@ -3201,10 +3178,10 @@
       <c r="A22" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="6">
         <v>2022.2</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="6">
         <v>12</v>
       </c>
     </row>
@@ -3212,10 +3189,10 @@
       <c r="A23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23">
         <v>447.5</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23">
         <v>2</v>
       </c>
     </row>
@@ -3223,10 +3200,10 @@
       <c r="A24" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24">
         <v>919.40000000000009</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24">
         <v>5</v>
       </c>
     </row>
@@ -3234,10 +3211,10 @@
       <c r="A25" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25">
         <v>268.7</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25">
         <v>2</v>
       </c>
     </row>
@@ -3245,10 +3222,10 @@
       <c r="A26" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26">
         <v>157</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26">
         <v>2</v>
       </c>
     </row>
@@ -3256,10 +3233,10 @@
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27">
         <v>229.6</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27">
         <v>1</v>
       </c>
     </row>
@@ -3267,10 +3244,10 @@
       <c r="A28" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28">
         <v>724.9</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28">
         <v>2</v>
       </c>
     </row>
@@ -3278,10 +3255,10 @@
       <c r="A29" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29">
         <v>724.9</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29">
         <v>2</v>
       </c>
     </row>
@@ -3289,24 +3266,20 @@
       <c r="A30" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32">
         <v>7897.2999999999984</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32">
         <v>40</v>
       </c>
     </row>
@@ -3326,10 +3299,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="6"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -3346,10 +3318,10 @@
       <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4">
         <v>9</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4">
         <v>1977.8</v>
       </c>
     </row>
@@ -3357,10 +3329,10 @@
       <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>8</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>915</v>
       </c>
     </row>
@@ -3368,10 +3340,10 @@
       <c r="A6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>14</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>2562.1000000000004</v>
       </c>
     </row>
@@ -3379,10 +3351,10 @@
       <c r="A7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7">
         <v>2442.3999999999996</v>
       </c>
     </row>
@@ -3390,17 +3362,15 @@
       <c r="A8" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>40</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9">
         <v>7897.3000000000011</v>
       </c>
     </row>
@@ -3447,16 +3417,16 @@
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4">
         <v>2258.6</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4">
         <v>2218.6</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4">
         <v>5.7142857142857144</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4">
         <v>0.98228991410608346</v>
       </c>
     </row>
@@ -3464,16 +3434,16 @@
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>289.5</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>284.5</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5">
         <v>1.6666666666666667</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5">
         <v>0.98272884283246975</v>
       </c>
     </row>
@@ -3481,16 +3451,16 @@
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>3263.4</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6">
         <v>3158.4</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6">
         <v>6.1764705882352944</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6">
         <v>0.96782496782496785</v>
       </c>
     </row>
@@ -3498,16 +3468,16 @@
       <c r="A7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>930.3</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7">
         <v>905.3</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7">
         <v>4.166666666666667</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7">
         <v>0.97312694829624857</v>
       </c>
     </row>
@@ -3515,16 +3485,16 @@
       <c r="A8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8">
         <v>366.7</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8">
         <v>331.7</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8">
         <v>11.666666666666666</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8">
         <v>0.90455413144259611</v>
       </c>
     </row>
@@ -3532,16 +3502,16 @@
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>1028.8</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9">
         <v>998.80000000000007</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9">
         <v>7.5</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9">
         <v>0.97083981337480574</v>
       </c>
     </row>
@@ -3549,10 +3519,7 @@
       <c r="A10" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7" t="e">
+      <c r="E10" t="e">
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3560,16 +3527,16 @@
       <c r="A11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11">
         <v>8137.2999999999993</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11">
         <v>7897.2999999999993</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11">
         <v>6</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11">
         <v>0.97050618755606899</v>
       </c>
     </row>
@@ -3580,10 +3547,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC6BE33-98F7-4742-820C-83A7AC2101A3}">
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="15" max="15" width="17.6640625" style="7" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3626,8 +3597,11 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -3670,8 +3644,12 @@
       <c r="N2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" s="7" t="str">
+        <f>VLOOKUP(K2, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -3714,8 +3692,12 @@
       <c r="N3">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" s="7" t="str">
+        <f>VLOOKUP(K3, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -3758,8 +3740,12 @@
       <c r="N4">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O4" s="7" t="str">
+        <f>VLOOKUP(K4, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -3802,8 +3788,12 @@
       <c r="N5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5" s="7" t="str">
+        <f>VLOOKUP(K5, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -3846,8 +3836,12 @@
       <c r="N6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6" s="7" t="str">
+        <f>VLOOKUP(K6, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -3890,8 +3884,12 @@
       <c r="N7">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7" s="7" t="str">
+        <f>VLOOKUP(K7, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -3934,8 +3932,12 @@
       <c r="N8">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" s="7" t="str">
+        <f>VLOOKUP(K8, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -3978,8 +3980,12 @@
       <c r="N9">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" s="7" t="str">
+        <f>VLOOKUP(K9, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Bronze</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -4022,8 +4028,12 @@
       <c r="N10">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10" s="7" t="str">
+        <f>VLOOKUP(K10, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -4066,8 +4076,12 @@
       <c r="N11">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O11" s="7" t="str">
+        <f>VLOOKUP(K11, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -4110,8 +4124,12 @@
       <c r="N12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O12" s="7" t="str">
+        <f>VLOOKUP(K12, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Bronze</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -4154,8 +4172,12 @@
       <c r="N13">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O13" s="7" t="str">
+        <f>VLOOKUP(K13, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -4198,8 +4220,12 @@
       <c r="N14">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14" s="7" t="str">
+        <f>VLOOKUP(K14, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -4242,8 +4268,12 @@
       <c r="N15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O15" s="7" t="str">
+        <f>VLOOKUP(K15, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>72</v>
       </c>
@@ -4286,8 +4316,12 @@
       <c r="N16">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O16" s="7" t="str">
+        <f>VLOOKUP(K16, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Bronze</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>73</v>
       </c>
@@ -4330,8 +4364,12 @@
       <c r="N17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O17" s="7" t="str">
+        <f>VLOOKUP(K17, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Bronze</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>74</v>
       </c>
@@ -4374,8 +4412,12 @@
       <c r="N18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O18" s="7" t="str">
+        <f>VLOOKUP(K18, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>75</v>
       </c>
@@ -4418,8 +4460,12 @@
       <c r="N19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O19" s="7" t="str">
+        <f>VLOOKUP(K19, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>76</v>
       </c>
@@ -4462,8 +4508,12 @@
       <c r="N20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O20" s="7" t="str">
+        <f>VLOOKUP(K20, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>77</v>
       </c>
@@ -4506,8 +4556,12 @@
       <c r="N21">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O21" s="7" t="str">
+        <f>VLOOKUP(K21, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>78</v>
       </c>
@@ -4550,8 +4604,12 @@
       <c r="N22">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O22" s="7" t="str">
+        <f>VLOOKUP(K22, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -4594,8 +4652,12 @@
       <c r="N23">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O23" s="7" t="str">
+        <f>VLOOKUP(K23, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -4638,8 +4700,12 @@
       <c r="N24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O24" s="7" t="str">
+        <f>VLOOKUP(K24, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -4682,8 +4748,12 @@
       <c r="N25">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O25" s="7" t="str">
+        <f>VLOOKUP(K25, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -4726,8 +4796,12 @@
       <c r="N26">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O26" s="7" t="str">
+        <f>VLOOKUP(K26, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>83</v>
       </c>
@@ -4770,8 +4844,12 @@
       <c r="N27">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O27" s="7" t="str">
+        <f>VLOOKUP(K27, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -4814,8 +4892,12 @@
       <c r="N28">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O28" s="7" t="str">
+        <f>VLOOKUP(K28, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Bronze</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -4858,8 +4940,12 @@
       <c r="N29">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O29" s="7" t="str">
+        <f>VLOOKUP(K29, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -4902,8 +4988,12 @@
       <c r="N30">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O30" s="7" t="str">
+        <f>VLOOKUP(K30, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>87</v>
       </c>
@@ -4946,8 +5036,12 @@
       <c r="N31">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O31" s="7" t="str">
+        <f>VLOOKUP(K31, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -4990,8 +5084,12 @@
       <c r="N32">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O32" s="7" t="str">
+        <f>VLOOKUP(K32, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -5034,8 +5132,12 @@
       <c r="N33">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O33" s="7" t="str">
+        <f>VLOOKUP(K33, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -5078,8 +5180,12 @@
       <c r="N34">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O34" s="7" t="str">
+        <f>VLOOKUP(K34, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>91</v>
       </c>
@@ -5122,8 +5228,12 @@
       <c r="N35">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O35" s="7" t="str">
+        <f>VLOOKUP(K35, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Bronze</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>92</v>
       </c>
@@ -5166,8 +5276,12 @@
       <c r="N36">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O36" s="7" t="str">
+        <f>VLOOKUP(K36, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>93</v>
       </c>
@@ -5210,8 +5324,12 @@
       <c r="N37">
         <v>3</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O37" s="7" t="str">
+        <f>VLOOKUP(K37, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Bronze</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>94</v>
       </c>
@@ -5254,8 +5372,12 @@
       <c r="N38">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O38" s="7" t="str">
+        <f>VLOOKUP(K38, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>95</v>
       </c>
@@ -5298,8 +5420,12 @@
       <c r="N39">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O39" s="7" t="str">
+        <f>VLOOKUP(K39, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>96</v>
       </c>
@@ -5342,8 +5468,12 @@
       <c r="N40">
         <v>4</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O40" s="7" t="str">
+        <f>VLOOKUP(K40, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Silver</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>97</v>
       </c>
@@ -5385,6 +5515,91 @@
       </c>
       <c r="N41">
         <v>4</v>
+      </c>
+      <c r="O41" s="7" t="str">
+        <f>VLOOKUP(K41, Seller_Lookup!$A$2:$C$6, 2, FALSE)</f>
+        <v>Gold</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7026339F-7483-4A07-B7CC-CC64DE199E77}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="7">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
